--- a/output/pdf_financials_xlsx/MIRA.xlsx
+++ b/output/pdf_financials_xlsx/MIRA.xlsx
@@ -631,10 +631,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.354421</v>
+        <v>-0.354421</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.199256</v>
+        <v>-0.199256</v>
       </c>
     </row>
     <row r="17">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.354421</v>
+        <v>-0.354421</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.199256</v>
+        <v>-0.199256</v>
       </c>
     </row>
     <row r="21">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.354421</v>
+        <v>-0.354421</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.199256</v>
+        <v>-0.199256</v>
       </c>
     </row>
     <row r="24">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-17.72105</v>
+        <v>17.72105</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.354421</v>
+        <v>-0.354421</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.199256</v>
+        <v>-0.199256</v>
       </c>
     </row>
     <row r="28">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.354421</v>
+        <v>-0.354421</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.199256</v>
+        <v>-0.199256</v>
       </c>
     </row>
     <row r="30">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.354421</v>
+        <v>-0.354421</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.199256</v>
+        <v>-0.199256</v>
       </c>
     </row>
     <row r="37">

--- a/output/pdf_financials_xlsx/MIRA.xlsx
+++ b/output/pdf_financials_xlsx/MIRA.xlsx
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.054692</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.060054</v>
       </c>
     </row>
     <row r="35">
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.054692</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.060054</v>
       </c>
     </row>
     <row r="37">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/MIRA.xlsx
+++ b/output/pdf_financials_xlsx/MIRA.xlsx
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.08018400000000001</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.231925</v>
       </c>
     </row>
     <row r="65">
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.0253</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="68">
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004754</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000616</v>
       </c>
     </row>
     <row r="102">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.040929</v>
+        <v>-0.045683</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.155234</v>
+        <v>0.154618</v>
       </c>
     </row>
     <row r="107">
@@ -2688,7 +2688,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>-0.004754</v>
       </c>
